--- a/planning/EPA_排程規劃.xlsx
+++ b/planning/EPA_排程規劃.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\004 教學資料 at Hsinchu 院內\Teaching materials CV education web at github\IM CCC EPA\planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63551759-42AB-45B8-8383-8B0E58188343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D117287-099B-4293-96B5-373DE2089D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表1_VS主治醫師名單" sheetId="1" r:id="rId1"/>
@@ -106,9 +106,6 @@
     <t>cv_epa</t>
   </si>
   <si>
-    <t>呂欣瑜</t>
-  </si>
-  <si>
     <t>sgps70632@gmail.com</t>
   </si>
   <si>
@@ -1099,6 +1096,10 @@
   </si>
   <si>
     <t>nephro_epa</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>呂欣瑜</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -1106,7 +1107,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1235,25 +1236,10 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1442,7 +1428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1543,40 +1529,34 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1597,7 +1577,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1626,7 +1606,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1647,36 +1627,36 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1982,7 +1962,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1993,18 +1973,18 @@
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-    </row>
-    <row r="2" spans="1:7" ht="36" customHeight="1">
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+    </row>
+    <row r="2" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2027,7 +2007,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18" customHeight="1">
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -2048,7 +2028,7 @@
       </c>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1">
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -2069,7 +2049,7 @@
       </c>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:7" ht="18" customHeight="1">
+    <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -2090,7 +2070,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="18" customHeight="1">
+    <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -2111,7 +2091,7 @@
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1">
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -2132,78 +2112,78 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1">
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="35" t="s">
+        <v>356</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>26</v>
+        <v>354</v>
       </c>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1">
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1">
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="D10" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="57" t="s">
-        <v>257</v>
+      <c r="F10" s="55" t="s">
+        <v>256</v>
       </c>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1">
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>25</v>
@@ -2216,36 +2196,36 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1">
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>38</v>
-      </c>
       <c r="D12" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="57" t="s">
-        <v>257</v>
+      <c r="F12" s="55" t="s">
+        <v>256</v>
       </c>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1">
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>10</v>
@@ -2258,36 +2238,36 @@
       </c>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1">
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="D14" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="57" t="s">
-        <v>257</v>
+      <c r="F14" s="55" t="s">
+        <v>256</v>
       </c>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1">
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>10</v>
@@ -2300,36 +2280,36 @@
       </c>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="1:7" ht="18" customHeight="1">
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:7" ht="18" customHeight="1">
+    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>21</v>
@@ -2342,15 +2322,15 @@
       </c>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="1:7" ht="18" customHeight="1">
+    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>25</v>
@@ -2363,78 +2343,78 @@
       </c>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:7" ht="18" customHeight="1">
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="D19" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:7" ht="18" customHeight="1">
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>18</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="D20" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="57" t="s">
-        <v>257</v>
+      <c r="F20" s="55" t="s">
+        <v>256</v>
       </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:7" ht="18" customHeight="1">
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="D21" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="1:7" ht="18" customHeight="1">
+    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>21</v>
@@ -2447,36 +2427,36 @@
       </c>
       <c r="G22" s="7"/>
     </row>
-    <row r="23" spans="1:7" ht="18" customHeight="1">
+    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="D23" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="1:7" ht="18" customHeight="1">
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>22</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>21</v>
@@ -2489,15 +2469,15 @@
       </c>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:7" ht="18" customHeight="1">
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>10</v>
@@ -2510,15 +2490,15 @@
       </c>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="1:7" ht="18" customHeight="1">
+    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>25</v>
@@ -2531,15 +2511,15 @@
       </c>
       <c r="G26" s="7"/>
     </row>
-    <row r="27" spans="1:7" ht="18" customHeight="1">
+    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>25</v>
@@ -2552,99 +2532,99 @@
       </c>
       <c r="G27" s="4"/>
     </row>
-    <row r="28" spans="1:7" ht="18" customHeight="1">
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>47</v>
+      <c r="D28" s="36" t="s">
+        <v>46</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G28" s="7"/>
     </row>
-    <row r="29" spans="1:7" ht="18" customHeight="1">
+    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G29" s="4"/>
     </row>
-    <row r="30" spans="1:7" ht="18" customHeight="1">
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>28</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30" s="35" t="s">
+      <c r="D30" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G30" s="8"/>
     </row>
-    <row r="31" spans="1:7" ht="18" customHeight="1">
+    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>29</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G31" s="4"/>
     </row>
-    <row r="32" spans="1:7" ht="18" customHeight="1">
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>30</v>
       </c>
       <c r="B32" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>21</v>
@@ -2657,78 +2637,78 @@
       </c>
       <c r="G32" s="7"/>
     </row>
-    <row r="33" spans="1:7" ht="18" customHeight="1">
+    <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>31</v>
       </c>
       <c r="B33" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>47</v>
+      <c r="D33" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G33" s="8"/>
     </row>
-    <row r="34" spans="1:7" ht="18" customHeight="1">
+    <row r="34" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>32</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>87</v>
-      </c>
       <c r="D34" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G34" s="7"/>
     </row>
-    <row r="35" spans="1:7" ht="18" customHeight="1">
+    <row r="35" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>33</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>81</v>
+      <c r="D35" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G35" s="4"/>
     </row>
-    <row r="36" spans="1:7" ht="18" customHeight="1">
+    <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>34</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>25</v>
@@ -2741,15 +2721,15 @@
       </c>
       <c r="G36" s="7"/>
     </row>
-    <row r="37" spans="1:7" ht="18" customHeight="1">
+    <row r="37" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>35</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>21</v>
@@ -2762,15 +2742,15 @@
       </c>
       <c r="G37" s="4"/>
     </row>
-    <row r="38" spans="1:7" ht="18" customHeight="1">
+    <row r="38" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>36</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>21</v>
@@ -2783,15 +2763,15 @@
       </c>
       <c r="G38" s="7"/>
     </row>
-    <row r="39" spans="1:7" ht="18" customHeight="1">
+    <row r="39" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>37</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>21</v>
@@ -2804,36 +2784,36 @@
       </c>
       <c r="G39" s="4"/>
     </row>
-    <row r="40" spans="1:7" ht="18" customHeight="1">
+    <row r="40" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>99</v>
-      </c>
       <c r="D40" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G40" s="7"/>
     </row>
-    <row r="41" spans="1:7" ht="18" customHeight="1">
+    <row r="41" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>39</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>25</v>
@@ -2846,36 +2826,36 @@
       </c>
       <c r="G41" s="4"/>
     </row>
-    <row r="42" spans="1:7" ht="18" customHeight="1">
+    <row r="42" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="D42" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G42" s="7"/>
     </row>
-    <row r="43" spans="1:7" ht="18" customHeight="1">
+    <row r="43" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>25</v>
@@ -2888,36 +2868,36 @@
       </c>
       <c r="G43" s="4"/>
     </row>
-    <row r="44" spans="1:7" ht="18" customHeight="1">
+    <row r="44" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>42</v>
       </c>
       <c r="B44" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C44" s="7" t="s">
-        <v>107</v>
-      </c>
       <c r="D44" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G44" s="7"/>
     </row>
-    <row r="45" spans="1:7" ht="18" customHeight="1">
+    <row r="45" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>43</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>10</v>
@@ -2930,36 +2910,36 @@
       </c>
       <c r="G45" s="4"/>
     </row>
-    <row r="46" spans="1:7" ht="18" customHeight="1">
+    <row r="46" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>44</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="D46" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G46" s="7"/>
     </row>
-    <row r="47" spans="1:7" ht="18" customHeight="1">
+    <row r="47" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>45</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>25</v>
@@ -2972,33 +2952,33 @@
       </c>
       <c r="G47" s="4"/>
     </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="67" t="s">
-        <v>114</v>
-      </c>
-      <c r="B49" s="68"/>
-      <c r="C49" s="68"/>
-      <c r="D49" s="68"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="68"/>
-      <c r="G49" s="68"/>
-    </row>
-    <row r="50" spans="1:7" ht="26" customHeight="1">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="65" t="s">
+        <v>113</v>
+      </c>
+      <c r="B49" s="66"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66"/>
+      <c r="G49" s="66"/>
+    </row>
+    <row r="50" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B50" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="11"/>
     </row>
-    <row r="51" spans="1:7" ht="18" customHeight="1">
+    <row r="51" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>25</v>
       </c>
@@ -3006,14 +2986,14 @@
         <v>10</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D51" s="15"/>
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
       <c r="G51" s="15"/>
     </row>
-    <row r="52" spans="1:7" ht="18" customHeight="1">
+    <row r="52" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
         <v>21</v>
       </c>
@@ -3021,29 +3001,29 @@
         <v>8</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D52" s="15"/>
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
       <c r="G52" s="15"/>
     </row>
-    <row r="53" spans="1:7" ht="18" customHeight="1">
+    <row r="53" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" s="13">
         <v>8</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D53" s="15"/>
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15"/>
     </row>
-    <row r="54" spans="1:7" ht="18" customHeight="1">
+    <row r="54" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
         <v>10</v>
       </c>
@@ -3051,14 +3031,14 @@
         <v>6</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D54" s="15"/>
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
       <c r="G54" s="15"/>
     </row>
-    <row r="55" spans="1:7" ht="18" customHeight="1">
+    <row r="55" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
         <v>17</v>
       </c>
@@ -3066,59 +3046,59 @@
         <v>3</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D55" s="15"/>
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
       <c r="G55" s="15"/>
     </row>
-    <row r="56" spans="1:7" ht="18" customHeight="1">
+    <row r="56" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B56" s="13">
         <v>4</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D56" s="15"/>
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15"/>
     </row>
-    <row r="57" spans="1:7" ht="18" customHeight="1">
+    <row r="57" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B57" s="13">
         <v>4</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D57" s="15"/>
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" s="15"/>
     </row>
-    <row r="58" spans="1:7" ht="18" customHeight="1">
+    <row r="58" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B58" s="13">
         <v>2</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D58" s="15"/>
       <c r="E58" s="15"/>
       <c r="F58" s="15"/>
       <c r="G58" s="15"/>
     </row>
-    <row r="59" spans="1:7" ht="18" customHeight="1">
+    <row r="59" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
         <v>17</v>
       </c>
@@ -3126,7 +3106,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D59" s="15"/>
       <c r="E59" s="15"/>
@@ -3147,7 +3127,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3159,829 +3139,829 @@
     <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="72" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-    </row>
-    <row r="2" spans="1:8" ht="36" customHeight="1">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+    </row>
+    <row r="2" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="G2" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="H2" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="H2" s="17" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1">
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="23" t="s">
         <v>126</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>127</v>
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="E4" s="23" t="s">
         <v>130</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>131</v>
       </c>
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1">
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>133</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1">
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="E6" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1">
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>138</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>140</v>
       </c>
       <c r="D8" s="33" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>142</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="D10" s="33" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>148</v>
-      </c>
       <c r="D12" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="33" t="s">
-        <v>151</v>
-      </c>
       <c r="E13" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>154</v>
-      </c>
       <c r="E14" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>158</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="D17" s="18" t="s">
-        <v>161</v>
-      </c>
       <c r="E17" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" ht="18" customHeight="1">
+    <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="18" t="s">
-        <v>164</v>
-      </c>
       <c r="E18" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" ht="18" customHeight="1">
+    <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="D19" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" ht="18" customHeight="1">
+    <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>18</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="D20" s="18" t="s">
         <v>17</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="18" customHeight="1">
+    <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="D21" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="H21" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="18" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>173</v>
-      </c>
       <c r="D22" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1">
+    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="D23" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F23" s="14"/>
       <c r="G23" s="14"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1">
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>22</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>177</v>
-      </c>
       <c r="D24" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1">
+    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>179</v>
       </c>
       <c r="D25" s="18" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1">
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>181</v>
-      </c>
       <c r="D26" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1">
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>183</v>
-      </c>
       <c r="D27" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1">
+    <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F28" s="14"/>
       <c r="G28" s="14"/>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8" ht="18" customHeight="1">
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>187</v>
-      </c>
       <c r="D29" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F29" s="14"/>
       <c r="G29" s="14"/>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" ht="18" customHeight="1">
+    <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>28</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>189</v>
-      </c>
       <c r="D30" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="18" customHeight="1">
+    <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>29</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="D31" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8" ht="18" customHeight="1">
+    <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>30</v>
       </c>
       <c r="B32" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="D32" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="D32" s="18" t="s">
-        <v>194</v>
-      </c>
       <c r="E32" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" ht="18" customHeight="1">
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>31</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="D33" s="18" t="s">
         <v>21</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" ht="18" customHeight="1">
+    <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>32</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>197</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>198</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" ht="18" customHeight="1">
+    <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>33</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>200</v>
-      </c>
       <c r="D35" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8" ht="18" customHeight="1">
+    <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>34</v>
       </c>
       <c r="B36" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>202</v>
-      </c>
       <c r="D36" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1">
+    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>35</v>
       </c>
       <c r="B37" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>204</v>
       </c>
       <c r="D37" s="18" t="s">
         <v>17</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F37" s="14"/>
       <c r="G37" s="14"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1">
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>36</v>
       </c>
       <c r="B38" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="D38" s="33" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F38" s="14"/>
       <c r="G38" s="14"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1">
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>37</v>
       </c>
       <c r="B39" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>17</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F39" s="14"/>
       <c r="G39" s="14"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" ht="18" customHeight="1">
+    <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>38</v>
       </c>
       <c r="B40" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>210</v>
-      </c>
       <c r="D40" s="33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E40" s="32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8" ht="18" customHeight="1">
+    <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>39</v>
       </c>
       <c r="B41" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="D41" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="D41" s="18" t="s">
-        <v>213</v>
-      </c>
       <c r="E41" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
       <c r="H41" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="18" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="25"/>
       <c r="B42" s="26"/>
       <c r="C42" s="27"/>
@@ -3991,53 +3971,53 @@
       <c r="G42" s="30"/>
       <c r="H42" s="27"/>
     </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="67" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="65" t="s">
+        <v>213</v>
+      </c>
+      <c r="B44" s="66"/>
+      <c r="C44" s="66"/>
+      <c r="D44" s="66"/>
+      <c r="E44" s="66"/>
+      <c r="F44" s="66"/>
+      <c r="G44" s="66"/>
+      <c r="H44" s="66"/>
+    </row>
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="68" t="s">
         <v>214</v>
       </c>
-      <c r="B44" s="68"/>
-      <c r="C44" s="68"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="68"/>
-      <c r="H44" s="68"/>
-    </row>
-    <row r="45" spans="1:8" ht="20" customHeight="1">
-      <c r="A45" s="70" t="s">
+      <c r="B45" s="66"/>
+      <c r="C45" s="66"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="66"/>
+      <c r="G45" s="66"/>
+      <c r="H45" s="66"/>
+    </row>
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="71" t="s">
         <v>215</v>
       </c>
-      <c r="B45" s="68"/>
-      <c r="C45" s="68"/>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
-      <c r="H45" s="68"/>
-    </row>
-    <row r="46" spans="1:8" ht="20" customHeight="1">
-      <c r="A46" s="73" t="s">
+      <c r="B46" s="66"/>
+      <c r="C46" s="66"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="66"/>
+      <c r="F46" s="66"/>
+      <c r="G46" s="66"/>
+      <c r="H46" s="66"/>
+    </row>
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="69" t="s">
         <v>216</v>
       </c>
-      <c r="B46" s="68"/>
-      <c r="C46" s="68"/>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
-      <c r="H46" s="68"/>
-    </row>
-    <row r="47" spans="1:8" ht="20" customHeight="1">
-      <c r="A47" s="71" t="s">
-        <v>217</v>
-      </c>
-      <c r="B47" s="68"/>
-      <c r="C47" s="68"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="68"/>
-      <c r="G47" s="68"/>
-      <c r="H47" s="68"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4063,7 +4043,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -4074,1580 +4054,1580 @@
     <col min="10" max="10" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="37" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="G2" s="38"/>
+    </row>
+    <row r="3" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="39" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="22" customHeight="1">
-      <c r="C2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="G2" s="40"/>
-    </row>
-    <row r="3" spans="1:10" ht="36" customHeight="1">
-      <c r="A3" s="41" t="s">
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+    </row>
+    <row r="4" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-    </row>
-    <row r="4" spans="1:10" ht="20" customHeight="1">
-      <c r="A4" s="43" t="s">
+      <c r="B4" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="C4" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
         <v>222</v>
       </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45" t="s">
+      <c r="B5" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="48" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="48" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="44" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="48" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="49"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="51"/>
+    </row>
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" s="50"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="51"/>
+    </row>
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>235</v>
+      </c>
+      <c r="E10" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="G10" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="H10" s="41" t="s">
+        <v>239</v>
+      </c>
+      <c r="I10" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="J10" s="52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I11" s="54" t="s">
+        <v>244</v>
+      </c>
+      <c r="J11" s="55"/>
+    </row>
+    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>204</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I12" s="54" t="s">
+        <v>244</v>
+      </c>
+      <c r="J12" s="55"/>
+    </row>
+    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="D13" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="55" t="s">
+        <v>245</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I13" s="54" t="s">
+        <v>244</v>
+      </c>
+      <c r="J13" s="55" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>185</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="55" t="s">
+        <v>247</v>
+      </c>
+      <c r="F14" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I14" s="54" t="s">
+        <v>244</v>
+      </c>
+      <c r="J14" s="55" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="B15" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="55" t="s">
+        <v>248</v>
+      </c>
+      <c r="F15" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I15" s="54" t="s">
+        <v>244</v>
+      </c>
+      <c r="J15" s="55" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="55" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="20" customHeight="1">
-      <c r="A5" s="46" t="s">
-        <v>223</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>224</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>225</v>
-      </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="50" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="20" customHeight="1">
-      <c r="A6" s="46" t="s">
-        <v>227</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>228</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>229</v>
-      </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="50" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="20" customHeight="1">
-      <c r="A7" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>231</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1">
-      <c r="A8" s="51"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
-    </row>
-    <row r="9" spans="1:10" ht="18" customHeight="1">
-      <c r="A9" s="41" t="s">
-        <v>233</v>
-      </c>
-      <c r="B9" s="52"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="53"/>
-    </row>
-    <row r="10" spans="1:10" ht="18" customHeight="1">
-      <c r="A10" s="43" t="s">
-        <v>220</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="C10" s="54" t="s">
-        <v>235</v>
-      </c>
-      <c r="D10" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>238</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>239</v>
-      </c>
-      <c r="H10" s="43" t="s">
-        <v>240</v>
-      </c>
-      <c r="I10" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J10" s="54" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="18" customHeight="1">
-      <c r="A11" s="55" t="s">
-        <v>242</v>
-      </c>
-      <c r="B11" s="56" t="s">
+      <c r="D16" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="H16" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="C11" s="57" t="s">
-        <v>178</v>
-      </c>
-      <c r="D11" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="56" t="s">
+      <c r="I16" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="J16" s="55"/>
+    </row>
+    <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="C17" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="H17" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I17" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="J17" s="55"/>
+    </row>
+    <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="B18" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="C18" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="55" t="s">
+        <v>254</v>
+      </c>
+      <c r="F18" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="H18" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I18" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="J18" s="55" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="55" t="s">
+        <v>256</v>
+      </c>
+      <c r="H19" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I19" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="J19" s="55"/>
+    </row>
+    <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="B20" s="54" t="s">
         <v>244</v>
       </c>
-      <c r="I11" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="J11" s="57"/>
-    </row>
-    <row r="12" spans="1:10" ht="18" customHeight="1">
-      <c r="A12" s="55" t="s">
-        <v>242</v>
-      </c>
-      <c r="B12" s="56" t="s">
+      <c r="C20" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="D20" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="55" t="s">
+        <v>258</v>
+      </c>
+      <c r="F20" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="56" t="s">
+        <v>256</v>
+      </c>
+      <c r="H20" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="C12" s="57" t="s">
-        <v>205</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="56" t="s">
+      <c r="I20" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="J20" s="55" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="B21" s="54" t="s">
         <v>244</v>
       </c>
-      <c r="I12" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="J12" s="57"/>
-    </row>
-    <row r="13" spans="1:10" ht="18" customHeight="1">
-      <c r="A13" s="55" t="s">
-        <v>242</v>
-      </c>
-      <c r="B13" s="56" t="s">
+      <c r="C21" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="55" t="s">
+        <v>260</v>
+      </c>
+      <c r="F21" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="56" t="s">
+        <v>256</v>
+      </c>
+      <c r="H21" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="C13" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="D13" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="57" t="s">
+      <c r="I21" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="J21" s="55" t="s">
         <v>246</v>
       </c>
-      <c r="F13" s="57" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="56" t="s">
+    </row>
+    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="B22" s="54" t="s">
         <v>244</v>
       </c>
-      <c r="I13" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="J13" s="57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="18" customHeight="1">
-      <c r="A14" s="55" t="s">
-        <v>242</v>
-      </c>
-      <c r="B14" s="56" t="s">
+      <c r="C22" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="55" t="s">
+        <v>261</v>
+      </c>
+      <c r="F22" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="55" t="s">
+        <v>256</v>
+      </c>
+      <c r="H22" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="C14" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="D14" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>248</v>
-      </c>
-      <c r="F14" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="57" t="s">
+      <c r="I22" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="J22" s="55" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>244</v>
+      </c>
+      <c r="C23" s="55" t="s">
+        <v>175</v>
+      </c>
+      <c r="D23" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I23" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="J23" s="55"/>
+    </row>
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="B24" s="54" t="s">
+        <v>244</v>
+      </c>
+      <c r="C24" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I24" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="J24" s="55"/>
+    </row>
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="C25" s="55" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="G25" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I25" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="J25" s="55" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="C26" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="D26" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I26" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="J26" s="55" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="B27" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="C27" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I27" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="J27" s="55"/>
+    </row>
+    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="C28" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I14" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="J14" s="57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="18" customHeight="1">
-      <c r="A15" s="55" t="s">
-        <v>242</v>
-      </c>
-      <c r="B15" s="56" t="s">
+      <c r="F28" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="C15" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="D15" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="57" t="s">
+      <c r="I28" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="J28" s="55"/>
+    </row>
+    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="C29" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="D29" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I29" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="J29" s="55"/>
+    </row>
+    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="C30" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="D30" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I30" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="J30" s="55" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="B31" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="C31" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I31" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="J31" s="55" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="B32" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="C32" s="55" t="s">
+        <v>208</v>
+      </c>
+      <c r="D32" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I32" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="J32" s="55" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="B33" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="C33" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="55" t="s">
+        <v>270</v>
+      </c>
+      <c r="F33" s="55" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I33" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="J33" s="55" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="B34" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="C34" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="D34" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="55" t="s">
+        <v>271</v>
+      </c>
+      <c r="F34" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="G34" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I34" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="J34" s="55" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="B35" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C35" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="D35" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="G35" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I35" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="B36" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C36" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="55" t="s">
+        <v>275</v>
+      </c>
+      <c r="F36" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I36" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="J36" s="55" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="B37" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C37" s="55" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="F37" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="G37" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I37" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="J37" s="55" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="B38" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="C38" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="55" t="s">
+        <v>270</v>
+      </c>
+      <c r="F38" s="55" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I38" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="J38" s="55" t="s">
         <v>249</v>
       </c>
-      <c r="F15" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H15" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I15" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="J15" s="57" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="18" customHeight="1">
-      <c r="A16" s="55" t="s">
-        <v>251</v>
-      </c>
-      <c r="B16" s="56" t="s">
-        <v>252</v>
-      </c>
-      <c r="C16" s="57" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="F16" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="G16" s="57" t="s">
-        <v>253</v>
-      </c>
-      <c r="H16" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I16" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="J16" s="57"/>
-    </row>
-    <row r="17" spans="1:10" ht="18" customHeight="1">
-      <c r="A17" s="55" t="s">
-        <v>251</v>
-      </c>
-      <c r="B17" s="56" t="s">
-        <v>252</v>
-      </c>
-      <c r="C17" s="57" t="s">
-        <v>180</v>
-      </c>
-      <c r="D17" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="57" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="57" t="s">
-        <v>253</v>
-      </c>
-      <c r="H17" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I17" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="J17" s="57"/>
-    </row>
-    <row r="18" spans="1:10" ht="18" customHeight="1">
-      <c r="A18" s="55" t="s">
-        <v>251</v>
-      </c>
-      <c r="B18" s="56" t="s">
-        <v>252</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>211</v>
-      </c>
-      <c r="D18" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="57" t="s">
+    </row>
+    <row r="39" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="B39" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="C39" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="D39" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="55" t="s">
+        <v>271</v>
+      </c>
+      <c r="F39" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="G39" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="I39" s="54" t="s">
+        <v>279</v>
+      </c>
+      <c r="J39" s="55" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="B40" s="57" t="s">
+        <v>268</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>210</v>
+      </c>
+      <c r="D40" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="58" t="s">
+        <v>280</v>
+      </c>
+      <c r="F40" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I40" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="J40" s="58" t="s">
         <v>255</v>
       </c>
-      <c r="F18" s="57" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="57" t="s">
-        <v>253</v>
-      </c>
-      <c r="H18" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I18" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="J18" s="57" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="18" customHeight="1">
-      <c r="A19" s="55" t="s">
-        <v>251</v>
-      </c>
-      <c r="B19" s="56" t="s">
-        <v>252</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="57" t="s">
-        <v>257</v>
-      </c>
-      <c r="H19" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I19" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="J19" s="57"/>
-    </row>
-    <row r="20" spans="1:10" ht="18" customHeight="1">
-      <c r="A20" s="55" t="s">
-        <v>258</v>
-      </c>
-      <c r="B20" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="C20" s="57" t="s">
-        <v>174</v>
-      </c>
-      <c r="D20" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="57" t="s">
-        <v>259</v>
-      </c>
-      <c r="F20" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" s="58" t="s">
-        <v>257</v>
-      </c>
-      <c r="H20" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I20" s="56" t="s">
-        <v>260</v>
-      </c>
-      <c r="J20" s="57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="18" customHeight="1">
-      <c r="A21" s="55" t="s">
-        <v>258</v>
-      </c>
-      <c r="B21" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>182</v>
-      </c>
-      <c r="D21" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="57" t="s">
-        <v>261</v>
-      </c>
-      <c r="F21" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="58" t="s">
-        <v>257</v>
-      </c>
-      <c r="H21" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I21" s="56" t="s">
-        <v>260</v>
-      </c>
-      <c r="J21" s="57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="18" customHeight="1">
-      <c r="A22" s="55" t="s">
-        <v>258</v>
-      </c>
-      <c r="B22" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="C22" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="57" t="s">
+    </row>
+    <row r="41" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="B41" s="57" t="s">
+        <v>268</v>
+      </c>
+      <c r="C41" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="D41" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I41" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="J41" s="58"/>
+    </row>
+    <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="B42" s="57" t="s">
+        <v>268</v>
+      </c>
+      <c r="C42" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I42" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="J42" s="58"/>
+    </row>
+    <row r="43" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="B43" s="57" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="D43" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="G43" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I43" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="J43" s="58"/>
+    </row>
+    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="53" t="s">
+        <v>281</v>
+      </c>
+      <c r="B44" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="C44" s="58" t="s">
+        <v>166</v>
+      </c>
+      <c r="D44" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I44" s="58" t="s">
+        <v>282</v>
+      </c>
+      <c r="J44" s="58" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="53" t="s">
+        <v>281</v>
+      </c>
+      <c r="B45" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="C45" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="D45" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I45" s="58" t="s">
+        <v>282</v>
+      </c>
+      <c r="J45" s="58" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="53" t="s">
+        <v>281</v>
+      </c>
+      <c r="B46" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="C46" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="D46" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="F46" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="G46" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I46" s="58" t="s">
+        <v>282</v>
+      </c>
+      <c r="J46" s="58" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="53" t="s">
+        <v>281</v>
+      </c>
+      <c r="B47" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="C47" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="D47" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I47" s="58" t="s">
+        <v>282</v>
+      </c>
+      <c r="J47" s="58" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="B48" s="57" t="s">
+        <v>279</v>
+      </c>
+      <c r="C48" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="G48" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I48" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="J48" s="58" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="B49" s="57" t="s">
+        <v>279</v>
+      </c>
+      <c r="C49" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="F49" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="G49" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I49" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="J49" s="58" t="s">
         <v>262</v>
       </c>
-      <c r="F22" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="G22" s="57" t="s">
-        <v>257</v>
-      </c>
-      <c r="H22" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I22" s="56" t="s">
-        <v>260</v>
-      </c>
-      <c r="J22" s="57" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="18" customHeight="1">
-      <c r="A23" s="55" t="s">
-        <v>258</v>
-      </c>
-      <c r="B23" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="C23" s="57" t="s">
-        <v>176</v>
-      </c>
-      <c r="D23" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="57" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="57" t="s">
-        <v>74</v>
-      </c>
-      <c r="G23" s="57" t="s">
-        <v>76</v>
-      </c>
-      <c r="H23" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I23" s="56" t="s">
-        <v>260</v>
-      </c>
-      <c r="J23" s="57"/>
-    </row>
-    <row r="24" spans="1:10" ht="18" customHeight="1">
-      <c r="A24" s="55" t="s">
-        <v>258</v>
-      </c>
-      <c r="B24" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="C24" s="57" t="s">
-        <v>199</v>
-      </c>
-      <c r="D24" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" s="57" t="s">
-        <v>110</v>
-      </c>
-      <c r="F24" s="57" t="s">
-        <v>111</v>
-      </c>
-      <c r="G24" s="57" t="s">
-        <v>76</v>
-      </c>
-      <c r="H24" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I24" s="56" t="s">
-        <v>260</v>
-      </c>
-      <c r="J24" s="57"/>
-    </row>
-    <row r="25" spans="1:10" ht="18" customHeight="1">
-      <c r="A25" s="55" t="s">
-        <v>264</v>
-      </c>
-      <c r="B25" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="C25" s="57" t="s">
-        <v>128</v>
-      </c>
-      <c r="D25" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="57" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" s="57" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" s="57" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I25" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="J25" s="57" t="s">
+    </row>
+    <row r="50" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="B50" s="57" t="s">
+        <v>279</v>
+      </c>
+      <c r="C50" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="D50" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I50" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="J50" s="58" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="18" customHeight="1">
-      <c r="A26" s="55" t="s">
-        <v>264</v>
-      </c>
-      <c r="B26" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="C26" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="D26" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="57" t="s">
-        <v>110</v>
-      </c>
-      <c r="F26" s="57" t="s">
-        <v>111</v>
-      </c>
-      <c r="G26" s="58" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I26" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="J26" s="57" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="18" customHeight="1">
-      <c r="A27" s="55" t="s">
-        <v>264</v>
-      </c>
-      <c r="B27" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="C27" s="57" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="58" t="s">
-        <v>22</v>
-      </c>
-      <c r="H27" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I27" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="J27" s="57"/>
-    </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1">
-      <c r="A28" s="55" t="s">
-        <v>264</v>
-      </c>
-      <c r="B28" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="C28" s="57" t="s">
-        <v>190</v>
-      </c>
-      <c r="D28" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="57" t="s">
-        <v>49</v>
-      </c>
-      <c r="F28" s="57" t="s">
-        <v>50</v>
-      </c>
-      <c r="G28" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I28" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="J28" s="57"/>
-    </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1">
-      <c r="A29" s="55" t="s">
-        <v>264</v>
-      </c>
-      <c r="B29" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="C29" s="57" t="s">
-        <v>195</v>
-      </c>
-      <c r="D29" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I29" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="J29" s="57"/>
-    </row>
-    <row r="30" spans="1:10" ht="18" customHeight="1">
-      <c r="A30" s="55" t="s">
-        <v>268</v>
-      </c>
-      <c r="B30" s="56" t="s">
-        <v>260</v>
-      </c>
-      <c r="C30" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="D30" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="F30" s="57" t="s">
-        <v>64</v>
-      </c>
-      <c r="G30" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I30" s="56" t="s">
-        <v>269</v>
-      </c>
-      <c r="J30" s="57" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="18" customHeight="1">
-      <c r="A31" s="55" t="s">
-        <v>268</v>
-      </c>
-      <c r="B31" s="56" t="s">
-        <v>260</v>
-      </c>
-      <c r="C31" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="D31" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="57" t="s">
-        <v>83</v>
-      </c>
-      <c r="G31" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I31" s="56" t="s">
-        <v>269</v>
-      </c>
-      <c r="J31" s="57" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="18" customHeight="1">
-      <c r="A32" s="55" t="s">
-        <v>268</v>
-      </c>
-      <c r="B32" s="56" t="s">
-        <v>260</v>
-      </c>
-      <c r="C32" s="57" t="s">
-        <v>209</v>
-      </c>
-      <c r="D32" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="57" t="s">
-        <v>92</v>
-      </c>
-      <c r="F32" s="57" t="s">
-        <v>93</v>
-      </c>
-      <c r="G32" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I32" s="56" t="s">
-        <v>269</v>
-      </c>
-      <c r="J32" s="57" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="18" customHeight="1">
-      <c r="A33" s="55" t="s">
-        <v>268</v>
-      </c>
-      <c r="B33" s="56" t="s">
-        <v>260</v>
-      </c>
-      <c r="C33" s="57" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="57" t="s">
-        <v>271</v>
-      </c>
-      <c r="F33" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="G33" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I33" s="56" t="s">
-        <v>269</v>
-      </c>
-      <c r="J33" s="57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1">
-      <c r="A34" s="55" t="s">
-        <v>268</v>
-      </c>
-      <c r="B34" s="56" t="s">
-        <v>260</v>
-      </c>
-      <c r="C34" s="57" t="s">
-        <v>139</v>
-      </c>
-      <c r="D34" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="57" t="s">
-        <v>272</v>
-      </c>
-      <c r="F34" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G34" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I34" s="56" t="s">
-        <v>269</v>
-      </c>
-      <c r="J34" s="57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1">
-      <c r="A35" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="B35" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="C35" s="57" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="57" t="s">
-        <v>274</v>
-      </c>
-      <c r="F35" s="57" t="s">
-        <v>64</v>
-      </c>
-      <c r="G35" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I35" s="56" t="s">
-        <v>275</v>
-      </c>
-      <c r="J35" s="57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="18" customHeight="1">
-      <c r="A36" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="B36" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="C36" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="D36" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="57" t="s">
-        <v>276</v>
-      </c>
-      <c r="F36" s="57" t="s">
-        <v>83</v>
-      </c>
-      <c r="G36" s="58" t="s">
-        <v>22</v>
-      </c>
-      <c r="H36" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I36" s="56" t="s">
-        <v>275</v>
-      </c>
-      <c r="J36" s="57" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="18" customHeight="1">
-      <c r="A37" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="B37" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="C37" s="57" t="s">
-        <v>184</v>
-      </c>
-      <c r="D37" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="57" t="s">
-        <v>278</v>
-      </c>
-      <c r="F37" s="57" t="s">
-        <v>93</v>
-      </c>
-      <c r="G37" s="58" t="s">
-        <v>22</v>
-      </c>
-      <c r="H37" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I37" s="56" t="s">
-        <v>275</v>
-      </c>
-      <c r="J37" s="57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="18" customHeight="1">
-      <c r="A38" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="B38" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="C38" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="D38" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="57" t="s">
-        <v>271</v>
-      </c>
-      <c r="F38" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="G38" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H38" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I38" s="56" t="s">
-        <v>275</v>
-      </c>
-      <c r="J38" s="57" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="18" customHeight="1">
-      <c r="A39" s="55" t="s">
+    <row r="51" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="B51" s="57" t="s">
         <v>279</v>
       </c>
-      <c r="B39" s="56" t="s">
-        <v>269</v>
-      </c>
-      <c r="C39" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="D39" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="57" t="s">
-        <v>272</v>
-      </c>
-      <c r="F39" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G39" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H39" s="56" t="s">
-        <v>244</v>
-      </c>
-      <c r="I39" s="56" t="s">
-        <v>280</v>
-      </c>
-      <c r="J39" s="57" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="18" customHeight="1">
-      <c r="A40" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="B40" s="59" t="s">
-        <v>269</v>
-      </c>
-      <c r="C40" s="60" t="s">
-        <v>211</v>
-      </c>
-      <c r="D40" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" s="60" t="s">
-        <v>281</v>
-      </c>
-      <c r="F40" s="60" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="H40" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I40" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="J40" s="60" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="18" customHeight="1">
-      <c r="A41" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="B41" s="59" t="s">
-        <v>269</v>
-      </c>
-      <c r="C41" s="60" t="s">
-        <v>141</v>
-      </c>
-      <c r="D41" s="60" t="s">
+      <c r="C51" s="58" t="s">
+        <v>210</v>
+      </c>
+      <c r="D51" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="E41" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41" s="60" t="s">
+      <c r="E51" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="G51" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="H41" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I41" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="J41" s="60"/>
-    </row>
-    <row r="42" spans="1:10" ht="18" customHeight="1">
-      <c r="A42" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="B42" s="59" t="s">
-        <v>269</v>
-      </c>
-      <c r="C42" s="60" t="s">
-        <v>203</v>
-      </c>
-      <c r="D42" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" s="60" t="s">
-        <v>29</v>
-      </c>
-      <c r="F42" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="G42" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="H42" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I42" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="J42" s="60"/>
-    </row>
-    <row r="43" spans="1:10" ht="18" customHeight="1">
-      <c r="A43" s="55" t="s">
-        <v>279</v>
-      </c>
-      <c r="B43" s="59" t="s">
-        <v>269</v>
-      </c>
-      <c r="C43" s="60" t="s">
-        <v>207</v>
-      </c>
-      <c r="D43" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="60" t="s">
-        <v>78</v>
-      </c>
-      <c r="G43" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="H43" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I43" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="J43" s="60"/>
-    </row>
-    <row r="44" spans="1:10" ht="18" customHeight="1">
-      <c r="A44" s="55" t="s">
-        <v>282</v>
-      </c>
-      <c r="B44" s="59" t="s">
-        <v>275</v>
-      </c>
-      <c r="C44" s="60" t="s">
-        <v>167</v>
-      </c>
-      <c r="D44" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="F44" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="H44" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I44" s="60" t="s">
-        <v>283</v>
-      </c>
-      <c r="J44" s="60" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="18" customHeight="1">
-      <c r="A45" s="55" t="s">
-        <v>282</v>
-      </c>
-      <c r="B45" s="59" t="s">
-        <v>275</v>
-      </c>
-      <c r="C45" s="60" t="s">
-        <v>155</v>
-      </c>
-      <c r="D45" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E45" s="60" t="s">
-        <v>29</v>
-      </c>
-      <c r="F45" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="G45" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="H45" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I45" s="60" t="s">
-        <v>283</v>
-      </c>
-      <c r="J45" s="60" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="18" customHeight="1">
-      <c r="A46" s="55" t="s">
-        <v>282</v>
-      </c>
-      <c r="B46" s="59" t="s">
-        <v>275</v>
-      </c>
-      <c r="C46" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="D46" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="F46" s="60" t="s">
-        <v>78</v>
-      </c>
-      <c r="G46" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I46" s="60" t="s">
-        <v>283</v>
-      </c>
-      <c r="J46" s="60" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="18" customHeight="1">
-      <c r="A47" s="55" t="s">
-        <v>282</v>
-      </c>
-      <c r="B47" s="59" t="s">
-        <v>275</v>
-      </c>
-      <c r="C47" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="D47" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="H47" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I47" s="60" t="s">
-        <v>283</v>
-      </c>
-      <c r="J47" s="60" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="18" customHeight="1">
-      <c r="A48" s="55" t="s">
+      <c r="H51" s="58" t="s">
+        <v>243</v>
+      </c>
+      <c r="I51" s="58" t="s">
         <v>284</v>
       </c>
-      <c r="B48" s="59" t="s">
-        <v>280</v>
-      </c>
-      <c r="C48" s="60" t="s">
-        <v>128</v>
-      </c>
-      <c r="D48" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" s="60" t="s">
-        <v>29</v>
-      </c>
-      <c r="F48" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="G48" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="H48" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I48" s="60" t="s">
+      <c r="J51" s="58" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="49"/>
+      <c r="B52" s="59"/>
+    </row>
+    <row r="53" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="J48" s="60" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="18" customHeight="1">
-      <c r="A49" s="55" t="s">
-        <v>284</v>
-      </c>
-      <c r="B49" s="59" t="s">
-        <v>280</v>
-      </c>
-      <c r="C49" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="D49" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="F49" s="60" t="s">
-        <v>78</v>
-      </c>
-      <c r="G49" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="H49" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I49" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="J49" s="60" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="18" customHeight="1">
-      <c r="A50" s="55" t="s">
-        <v>284</v>
-      </c>
-      <c r="B50" s="59" t="s">
-        <v>280</v>
-      </c>
-      <c r="C50" s="60" t="s">
-        <v>162</v>
-      </c>
-      <c r="D50" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="G50" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="H50" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I50" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="J50" s="60" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="18" customHeight="1">
-      <c r="A51" s="55" t="s">
-        <v>284</v>
-      </c>
-      <c r="B51" s="59" t="s">
-        <v>280</v>
-      </c>
-      <c r="C51" s="60" t="s">
-        <v>211</v>
-      </c>
-      <c r="D51" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="60" t="s">
-        <v>29</v>
-      </c>
-      <c r="F51" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="G51" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="H51" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="I51" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="J51" s="60" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="18" customHeight="1">
-      <c r="A52" s="51"/>
-      <c r="B52" s="61"/>
-    </row>
-    <row r="53" spans="1:10" ht="18" customHeight="1">
-      <c r="A53" s="41" t="s">
+      <c r="B53" s="59"/>
+    </row>
+    <row r="54" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="60" t="s">
         <v>286</v>
       </c>
-      <c r="B53" s="61"/>
-    </row>
-    <row r="54" spans="1:10" ht="18" customHeight="1">
-      <c r="A54" s="62" t="s">
+      <c r="B54" s="61" t="s">
         <v>287</v>
       </c>
-      <c r="B54" s="63" t="s">
+      <c r="C54" s="62"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="62"/>
+      <c r="F54" s="62"/>
+      <c r="G54" s="62"/>
+      <c r="H54" s="62"/>
+      <c r="I54" s="62"/>
+      <c r="J54" s="62"/>
+    </row>
+    <row r="55" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="60" t="s">
         <v>288</v>
       </c>
-      <c r="C54" s="64"/>
-      <c r="D54" s="64"/>
-      <c r="E54" s="64"/>
-      <c r="F54" s="64"/>
-      <c r="G54" s="64"/>
-      <c r="H54" s="64"/>
-      <c r="I54" s="64"/>
-      <c r="J54" s="64"/>
-    </row>
-    <row r="55" spans="1:10" ht="18" customHeight="1">
-      <c r="A55" s="62" t="s">
+      <c r="B55" s="61" t="s">
+        <v>287</v>
+      </c>
+      <c r="C55" s="62"/>
+      <c r="D55" s="62"/>
+      <c r="E55" s="62"/>
+      <c r="F55" s="62"/>
+      <c r="G55" s="62"/>
+      <c r="H55" s="62"/>
+      <c r="I55" s="62"/>
+      <c r="J55" s="62"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="62" t="s">
         <v>289</v>
       </c>
-      <c r="B55" s="63" t="s">
-        <v>288</v>
-      </c>
-      <c r="C55" s="64"/>
-      <c r="D55" s="64"/>
-      <c r="E55" s="64"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="64"/>
-      <c r="I55" s="64"/>
-      <c r="J55" s="64"/>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="64" t="s">
+      <c r="B56" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="C56" s="62"/>
+      <c r="D56" s="62"/>
+      <c r="E56" s="62"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="62"/>
+      <c r="H56" s="62"/>
+      <c r="I56" s="62"/>
+      <c r="J56" s="62"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="62" t="s">
         <v>290</v>
       </c>
-      <c r="B56" s="64" t="s">
-        <v>288</v>
-      </c>
-      <c r="C56" s="64"/>
-      <c r="D56" s="64"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="64"/>
-      <c r="G56" s="64"/>
-      <c r="H56" s="64"/>
-      <c r="I56" s="64"/>
-      <c r="J56" s="64"/>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="64" t="s">
+      <c r="B57" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="C57" s="62"/>
+      <c r="D57" s="62"/>
+      <c r="E57" s="62"/>
+      <c r="F57" s="62"/>
+      <c r="G57" s="62"/>
+      <c r="H57" s="62"/>
+      <c r="I57" s="62"/>
+      <c r="J57" s="62"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="62" t="s">
         <v>291</v>
       </c>
-      <c r="B57" s="64" t="s">
-        <v>288</v>
-      </c>
-      <c r="C57" s="64"/>
-      <c r="D57" s="64"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
-      <c r="H57" s="64"/>
-      <c r="I57" s="64"/>
-      <c r="J57" s="64"/>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="64" t="s">
+      <c r="B58" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="C58" s="62"/>
+      <c r="D58" s="62"/>
+      <c r="E58" s="62"/>
+      <c r="F58" s="62"/>
+      <c r="G58" s="62"/>
+      <c r="H58" s="62"/>
+      <c r="I58" s="62"/>
+      <c r="J58" s="62"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="62" t="s">
         <v>292</v>
       </c>
-      <c r="B58" s="64" t="s">
-        <v>288</v>
-      </c>
-      <c r="C58" s="64"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="64"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="64"/>
-      <c r="J58" s="64"/>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="64" t="s">
+      <c r="B59" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="C59" s="62"/>
+      <c r="D59" s="62"/>
+      <c r="E59" s="62"/>
+      <c r="F59" s="62"/>
+      <c r="G59" s="62"/>
+      <c r="H59" s="62"/>
+      <c r="I59" s="62"/>
+      <c r="J59" s="62"/>
+    </row>
+    <row r="61" spans="1:10" ht="17" x14ac:dyDescent="0.4">
+      <c r="A61" s="63" t="s">
         <v>293</v>
       </c>
-      <c r="B59" s="64" t="s">
-        <v>288</v>
-      </c>
-      <c r="C59" s="64"/>
-      <c r="D59" s="64"/>
-      <c r="E59" s="64"/>
-      <c r="F59" s="64"/>
-      <c r="G59" s="64"/>
-      <c r="H59" s="64"/>
-      <c r="I59" s="64"/>
-      <c r="J59" s="64"/>
-    </row>
-    <row r="61" spans="1:10" ht="17">
-      <c r="A61" s="65" t="s">
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="64" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="66" t="s">
+      <c r="B62" s="64" t="s">
         <v>295</v>
       </c>
-      <c r="B62" s="66" t="s">
-        <v>296</v>
-      </c>
-      <c r="C62" s="66"/>
-      <c r="D62" s="66"/>
-      <c r="E62" s="66"/>
-      <c r="F62" s="66"/>
-      <c r="G62" s="66"/>
-      <c r="H62" s="66"/>
-      <c r="I62" s="66"/>
-      <c r="J62" s="66"/>
+      <c r="C62" s="64"/>
+      <c r="D62" s="64"/>
+      <c r="E62" s="64"/>
+      <c r="F62" s="64"/>
+      <c r="G62" s="64"/>
+      <c r="H62" s="64"/>
+      <c r="I62" s="64"/>
+      <c r="J62" s="64"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -5658,7 +5638,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
@@ -5667,47 +5647,47 @@
     <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="72" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+    </row>
+    <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="79" t="s">
         <v>297</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-    </row>
-    <row r="3" spans="1:6" ht="24" customHeight="1">
-      <c r="A3" s="81" t="s">
-        <v>298</v>
-      </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-    </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+    </row>
+    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="20" customHeight="1">
+    </row>
+    <row r="5" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>25</v>
       </c>
@@ -5715,7 +5695,7 @@
         <v>26</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" s="13">
         <v>9</v>
@@ -5724,10 +5704,10 @@
         <v>3</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="20" customHeight="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>21</v>
       </c>
@@ -5735,7 +5715,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" s="13">
         <v>8</v>
@@ -5744,18 +5724,18 @@
         <v>14</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="20" customHeight="1">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>48</v>
-      </c>
       <c r="C7" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" s="13">
         <v>7</v>
@@ -5764,18 +5744,18 @@
         <v>2</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="20" customHeight="1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>76</v>
-      </c>
       <c r="C8" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8" s="13">
         <v>2</v>
@@ -5784,10 +5764,10 @@
         <v>4</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="20" customHeight="1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>17</v>
       </c>
@@ -5795,7 +5775,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D9" s="13">
         <v>1</v>
@@ -5804,10 +5784,10 @@
         <v>11</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="20" customHeight="1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>10</v>
       </c>
@@ -5815,7 +5795,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D10" s="13">
         <v>5</v>
@@ -5824,18 +5804,18 @@
         <v>0</v>
       </c>
       <c r="F10" s="12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="20" customHeight="1">
-      <c r="A11" s="20" t="s">
+      <c r="B11" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="C11" s="14" t="s">
         <v>309</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>310</v>
       </c>
       <c r="D11" s="13">
         <v>0</v>
@@ -5844,18 +5824,18 @@
         <v>0</v>
       </c>
       <c r="F11" s="12" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>311</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="20" customHeight="1">
-      <c r="A12" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>312</v>
       </c>
       <c r="D12" s="13">
         <v>4</v>
@@ -5864,247 +5844,259 @@
         <v>4</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="20" customHeight="1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D13" s="13">
         <v>4</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="12" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="65" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
-      <c r="A15" s="67" t="s">
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="10" t="s">
+      <c r="B16" s="81" t="s">
         <v>316</v>
       </c>
-      <c r="B16" s="84" t="s">
+      <c r="C16" s="74"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="81" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" s="75"/>
+    </row>
+    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C16" s="77"/>
-      <c r="D16" s="75"/>
-      <c r="E16" s="84" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16" s="75"/>
-    </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="77" t="s">
         <v>318</v>
       </c>
-      <c r="B17" s="76" t="s">
-        <v>319</v>
-      </c>
-      <c r="C17" s="77"/>
+      <c r="C17" s="74"/>
       <c r="D17" s="75"/>
       <c r="E17" s="78" t="s">
+        <v>319</v>
+      </c>
+      <c r="F17" s="75"/>
+    </row>
+    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="F17" s="75"/>
-    </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1">
-      <c r="A18" s="13" t="s">
+      <c r="B18" s="73" t="s">
         <v>321</v>
       </c>
-      <c r="B18" s="79" t="s">
+      <c r="C18" s="74"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="76" t="s">
         <v>322</v>
       </c>
-      <c r="C18" s="77"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="82" t="s">
+      <c r="F18" s="75"/>
+    </row>
+    <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F18" s="75"/>
-    </row>
-    <row r="19" spans="1:6" ht="22" customHeight="1">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="77" t="s">
         <v>324</v>
       </c>
-      <c r="B19" s="76" t="s">
-        <v>325</v>
-      </c>
-      <c r="C19" s="77"/>
+      <c r="C19" s="74"/>
       <c r="D19" s="75"/>
       <c r="E19" s="78" t="s">
+        <v>325</v>
+      </c>
+      <c r="F19" s="75"/>
+    </row>
+    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="F19" s="75"/>
-    </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1">
-      <c r="A20" s="13" t="s">
+      <c r="B20" s="73" t="s">
         <v>327</v>
       </c>
-      <c r="B20" s="79" t="s">
+      <c r="C20" s="74"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="76" t="s">
         <v>328</v>
       </c>
-      <c r="C20" s="77"/>
-      <c r="D20" s="75"/>
-      <c r="E20" s="82" t="s">
+      <c r="F20" s="75"/>
+    </row>
+    <row r="21" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="F20" s="75"/>
-    </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1">
-      <c r="A21" s="2" t="s">
+      <c r="B21" s="77" t="s">
         <v>330</v>
       </c>
-      <c r="B21" s="76" t="s">
-        <v>331</v>
-      </c>
-      <c r="C21" s="77"/>
+      <c r="C21" s="74"/>
       <c r="D21" s="75"/>
       <c r="E21" s="78" t="s">
+        <v>331</v>
+      </c>
+      <c r="F21" s="75"/>
+    </row>
+    <row r="22" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="F21" s="75"/>
-    </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1">
-      <c r="A22" s="13" t="s">
+      <c r="B22" s="73" t="s">
         <v>333</v>
       </c>
-      <c r="B22" s="79" t="s">
+      <c r="C22" s="74"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="76" t="s">
         <v>334</v>
       </c>
-      <c r="C22" s="77"/>
-      <c r="D22" s="75"/>
-      <c r="E22" s="82" t="s">
+      <c r="F22" s="75"/>
+    </row>
+    <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F22" s="75"/>
-    </row>
-    <row r="23" spans="1:6" ht="22" customHeight="1">
-      <c r="A23" s="2" t="s">
+      <c r="B23" s="77" t="s">
         <v>336</v>
       </c>
-      <c r="B23" s="76" t="s">
-        <v>337</v>
-      </c>
-      <c r="C23" s="77"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="75"/>
       <c r="E23" s="78" t="s">
+        <v>337</v>
+      </c>
+      <c r="F23" s="75"/>
+    </row>
+    <row r="24" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="F23" s="75"/>
-    </row>
-    <row r="24" spans="1:6" ht="22" customHeight="1">
-      <c r="A24" s="21" t="s">
+      <c r="B24" s="80" t="s">
         <v>339</v>
       </c>
-      <c r="B24" s="83" t="s">
+      <c r="C24" s="74"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="82" t="s">
         <v>340</v>
       </c>
-      <c r="C24" s="77"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="74" t="s">
+      <c r="F24" s="75"/>
+    </row>
+    <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="83" t="s">
         <v>341</v>
       </c>
-      <c r="F24" s="75"/>
-    </row>
-    <row r="26" spans="1:6" ht="24" customHeight="1">
-      <c r="A26" s="80" t="s">
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="75"/>
+    </row>
+    <row r="27" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
         <v>342</v>
       </c>
-      <c r="B26" s="77"/>
-      <c r="C26" s="77"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="75"/>
-    </row>
-    <row r="27" spans="1:6" ht="20" customHeight="1">
-      <c r="A27" s="22" t="s">
+      <c r="B27" s="73" t="s">
         <v>343</v>
       </c>
-      <c r="B27" s="79" t="s">
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="75"/>
+    </row>
+    <row r="28" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="75"/>
-    </row>
-    <row r="28" spans="1:6" ht="20" customHeight="1">
-      <c r="A28" s="22" t="s">
+      <c r="B28" s="73" t="s">
         <v>345</v>
       </c>
-      <c r="B28" s="79" t="s">
+      <c r="C28" s="74"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="75"/>
+    </row>
+    <row r="29" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="75"/>
-    </row>
-    <row r="29" spans="1:6" ht="20" customHeight="1">
-      <c r="A29" s="22" t="s">
+      <c r="B29" s="73" t="s">
         <v>347</v>
       </c>
-      <c r="B29" s="79" t="s">
+      <c r="C29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="75"/>
+    </row>
+    <row r="30" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="22" t="s">
         <v>348</v>
       </c>
-      <c r="C29" s="77"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="75"/>
-    </row>
-    <row r="30" spans="1:6" ht="20" customHeight="1">
-      <c r="A30" s="22" t="s">
+      <c r="B30" s="73" t="s">
         <v>349</v>
       </c>
-      <c r="B30" s="79" t="s">
+      <c r="C30" s="74"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="75"/>
+    </row>
+    <row r="31" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="22" t="s">
         <v>350</v>
       </c>
-      <c r="C30" s="77"/>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="75"/>
-    </row>
-    <row r="31" spans="1:6" ht="20" customHeight="1">
-      <c r="A31" s="22" t="s">
+      <c r="B31" s="73" t="s">
         <v>351</v>
       </c>
-      <c r="B31" s="79" t="s">
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="75"/>
+    </row>
+    <row r="32" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="C31" s="77"/>
-      <c r="D31" s="77"/>
-      <c r="E31" s="77"/>
-      <c r="F31" s="75"/>
-    </row>
-    <row r="32" spans="1:6" ht="20" customHeight="1">
-      <c r="A32" s="22" t="s">
+      <c r="B32" s="73" t="s">
         <v>353</v>
       </c>
-      <c r="B32" s="79" t="s">
-        <v>354</v>
-      </c>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
+      <c r="C32" s="74"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
       <c r="F32" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E23:F23"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E22:F22"/>
@@ -6121,18 +6113,6 @@
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B30:F30"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
